--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6412-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6412-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89634E15-FDC2-4771-BA3B-CC304DD2A9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8FF863B-8DA8-42F1-9369-E46752CC8997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{AABF0D4B-0DDF-4AF2-A585-859F62565B49}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{2F208E5B-435A-4C88-B7B1-7BF75B0F7640}"/>
   </bookViews>
   <sheets>
     <sheet name="6412-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1532,29 +1532,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CCBD0BC-4630-494D-B1AB-D4B8E0C6987D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8B599B8-01A5-44F5-A5BD-A84325AED80E}">
   <dimension ref="A1:X23"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1588,7 +1587,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1624,7 +1623,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1676,7 +1675,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1744,7 +1743,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1816,7 +1815,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1888,7 +1887,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1960,7 +1959,7 @@
         <v>8.08</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2032,7 +2031,7 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2104,7 +2103,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2176,7 +2175,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2248,7 +2247,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="41">
         <v>2017</v>
       </c>
@@ -2320,7 +2319,7 @@
         <v>8.31</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="43"/>
       <c r="B13" s="44"/>
       <c r="C13" s="18" t="s">
@@ -2348,7 +2347,7 @@
       <c r="W13" s="50"/>
       <c r="X13" s="46"/>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="51">
         <v>2016</v>
       </c>
@@ -2420,7 +2419,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="53"/>
       <c r="B15" s="54"/>
       <c r="C15" s="20" t="s">
@@ -2448,7 +2447,7 @@
       <c r="W15" s="60"/>
       <c r="X15" s="56"/>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="41">
         <v>2015</v>
       </c>
@@ -2520,7 +2519,7 @@
         <v>7.11</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="43"/>
       <c r="B17" s="44"/>
       <c r="C17" s="18" t="s">
@@ -2548,7 +2547,7 @@
       <c r="W17" s="50"/>
       <c r="X17" s="46"/>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="51">
         <v>2014</v>
       </c>
@@ -2620,7 +2619,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="53"/>
       <c r="B19" s="54"/>
       <c r="C19" s="20" t="s">
@@ -2648,7 +2647,7 @@
       <c r="W19" s="60"/>
       <c r="X19" s="56"/>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="41">
         <v>2013</v>
       </c>
@@ -2720,7 +2719,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="43"/>
       <c r="B21" s="44"/>
       <c r="C21" s="18" t="s">
@@ -2748,7 +2747,7 @@
       <c r="W21" s="50"/>
       <c r="X21" s="46"/>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2012</v>
       </c>
@@ -2820,7 +2819,7 @@
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39" t="s">
         <v>46</v>
       </c>
